--- a/SHOP_Qcut_開戶至交易日數.xlsx
+++ b/SHOP_Qcut_開戶至交易日數.xlsx
@@ -413,36 +413,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>SHAP_Min</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>SHAP_Max</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Feature_Mean</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SHAP_Mean</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>SHAP_Median</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>SHAP_Std</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Fraud_Prob</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Cnt</t>
         </is>
@@ -450,201 +460,261 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>-1.060999989509583</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.7609999775886536</v>
+      </c>
+      <c r="C2" t="n">
         <v>238.916</v>
       </c>
-      <c r="B2" t="n">
+      <c r="D2" t="n">
         <v>-0.05820000171661377</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>-0.01549999974668026</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>0.3544999957084656</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>0.8628000020980835</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>1429</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>-1.402699947357178</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.8156999945640564</v>
+      </c>
+      <c r="C3" t="n">
         <v>427.9671</v>
       </c>
-      <c r="B3" t="n">
+      <c r="D3" t="n">
         <v>0.06840000301599503</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>0.1396999955177307</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>0.3648000061511993</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>0.863099992275238</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>1397</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>-1.07669997215271</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5356000065803528</v>
+      </c>
+      <c r="C4" t="n">
         <v>1015.0943</v>
       </c>
-      <c r="B4" t="n">
+      <c r="D4" t="n">
         <v>-0.2111999988555908</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>-0.1791000068187714</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>0.328000009059906</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>0.868399977684021</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>1411</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>-1.146700024604797</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9211999773979187</v>
+      </c>
+      <c r="C5" t="n">
         <v>1734.8257</v>
       </c>
-      <c r="B5" t="n">
+      <c r="D5" t="n">
         <v>-0.2012999951839447</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>-0.1529999971389771</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>0.4293000102043152</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>0.8686000108718872</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>1406</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>-0.4156000018119812</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1.518700003623962</v>
+      </c>
+      <c r="C6" t="n">
         <v>2930.3232</v>
       </c>
-      <c r="B6" t="n">
+      <c r="D6" t="n">
         <v>0.5241000056266785</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>0.6347000002861023</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>0.4846000075340271</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>0.8611999750137329</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>1408</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>-1.09469997882843</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9488999843597412</v>
+      </c>
+      <c r="C7" t="n">
         <v>4680.5262</v>
       </c>
-      <c r="B7" t="n">
+      <c r="D7" t="n">
         <v>-0.118199996650219</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>-0.1098999977111816</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>0.3244999945163727</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>0.8722000122070312</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>1414</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>0.02429999969899654</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1.040599942207336</v>
+      </c>
+      <c r="C8" t="n">
         <v>6696.0775</v>
       </c>
-      <c r="B8" t="n">
+      <c r="D8" t="n">
         <v>0.696399986743927</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>0.7243999838829041</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>0.1438000053167343</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>0.8608999848365784</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
         <v>1406</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>0.1356000006198883</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1.400099992752075</v>
+      </c>
+      <c r="C9" t="n">
         <v>6904.2034</v>
       </c>
-      <c r="B9" t="n">
+      <c r="D9" t="n">
         <v>0.8776000142097473</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>0.8769999742507935</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>0.1782000064849854</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>0.8639000058174133</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>1416</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>0.2330999970436096</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1.442999958992004</v>
+      </c>
+      <c r="C10" t="n">
         <v>7068.4844</v>
       </c>
-      <c r="B10" t="n">
+      <c r="D10" t="n">
         <v>0.9228000044822693</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>0.9341999888420105</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>0.1720000058412552</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>0.8654999732971191</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
         <v>1408</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>-2.073999881744385</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1.973199963569641</v>
+      </c>
+      <c r="C11" t="n">
         <v>7878.7775</v>
       </c>
-      <c r="B11" t="n">
+      <c r="D11" t="n">
         <v>0.4751999974250793</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>0.6086000204086304</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>0.541700005531311</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>0.8628000020980835</v>
       </c>
-      <c r="F11" t="n">
+      <c r="H11" t="n">
         <v>1407</v>
       </c>
     </row>
